--- a/_qa/006_Actions_Tests.xlsx
+++ b/_qa/006_Actions_Tests.xlsx
@@ -1,37 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_source\Greenshoes\quodsi_lucidchart_package\_qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E902A8-AF05-4B00-9574-A631E5EC14B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actions" sheetId="8" r:id="rId1"/>
     <sheet name="Action Validation" sheetId="9" r:id="rId2"/>
-    <sheet name="Assign Action" sheetId="10" r:id="rId6"/>
-    <sheet name="Seize Action" sheetId="11" r:id="rId7"/>
-    <sheet name="Release Action" sheetId="12" r:id="rId8"/>
-    <sheet name="Delay Action" sheetId="13" r:id="rId9"/>
-    <sheet name="Delay With Resource" sheetId="14" r:id="rId10"/>
-    <sheet name="Split Action" sheetId="15" r:id="rId11"/>
-    <sheet name="Create Action" sheetId="16" r:id="rId12"/>
-    <sheet name="Dispose Action" sheetId="17" r:id="rId13"/>
-    <sheet name="Join Action" sheetId="18" r:id="rId14"/>
-    <sheet name="Loop Action" sheetId="19" r:id="rId15"/>
-    <sheet name="Branch Action" sheetId="20" r:id="rId16"/>
+    <sheet name="Assign Action" sheetId="10" r:id="rId3"/>
+    <sheet name="Seize Action" sheetId="11" r:id="rId4"/>
+    <sheet name="Release Action" sheetId="12" r:id="rId5"/>
+    <sheet name="Delay Action" sheetId="13" r:id="rId6"/>
+    <sheet name="Delay With Resource" sheetId="14" r:id="rId7"/>
+    <sheet name="Split Action" sheetId="15" r:id="rId8"/>
+    <sheet name="Create Action" sheetId="16" r:id="rId9"/>
+    <sheet name="Dispose Action" sheetId="17" r:id="rId10"/>
+    <sheet name="Join Action" sheetId="18" r:id="rId11"/>
+    <sheet name="Loop Action" sheetId="19" r:id="rId12"/>
+    <sheet name="Branch Action" sheetId="20" r:id="rId13"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="662">
   <si>
     <t>P1</t>
   </si>
@@ -2776,25 +2777,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
     </font>
   </fonts>
   <fills count="2">
@@ -2817,18 +2819,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2841,7 +2847,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3124,7 +3130,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2957E501-C807-467F-94F9-1F488031F3C0}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3706,10 +3712,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6A2B7A-111D-4B97-B493-07FCA5859522}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -3753,15 +3760,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>465</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>466</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>467</v>
       </c>
       <c r="D2" t="s">
         <v>141</v>
@@ -3770,10 +3777,10 @@
         <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>468</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>469</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -3797,27 +3804,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>470</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>471</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>472</v>
       </c>
       <c r="D3" t="s">
         <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>149</v>
+        <v>473</v>
       </c>
       <c r="F3" t="s">
-        <v>150</v>
+        <v>474</v>
       </c>
       <c r="G3" t="s">
-        <v>151</v>
+        <v>475</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -3841,27 +3848,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>476</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>398</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>477</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>478</v>
       </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>479</v>
       </c>
       <c r="G4" t="s">
-        <v>158</v>
+        <v>480</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -3885,27 +3892,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>481</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>482</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>483</v>
       </c>
       <c r="D5" t="s">
         <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>484</v>
       </c>
       <c r="F5" t="s">
-        <v>163</v>
+        <v>485</v>
       </c>
       <c r="G5" t="s">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -3929,115 +3936,115 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>487</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>488</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>489</v>
       </c>
       <c r="D6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" t="s">
+        <v>491</v>
+      </c>
+      <c r="G6" t="s">
+        <v>492</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>493</v>
+      </c>
+      <c r="B7" t="s">
+        <v>494</v>
+      </c>
+      <c r="C7" t="s">
+        <v>495</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>496</v>
+      </c>
+      <c r="F7" t="s">
+        <v>497</v>
+      </c>
+      <c r="G7" t="s">
+        <v>498</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C8" t="s">
+        <v>501</v>
+      </c>
+      <c r="D8" t="s">
         <v>168</v>
       </c>
-      <c r="E6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" t="s">
-        <v>170</v>
-      </c>
-      <c r="G6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" t="s">
-        <v>155</v>
-      </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>410</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>502</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>503</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -4061,59 +4068,17 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{510AE1B1-B0B6-420A-A25B-1589B4220733}">
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -4157,15 +4122,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>504</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>505</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>506</v>
       </c>
       <c r="D2" t="s">
         <v>141</v>
@@ -4174,10 +4139,10 @@
         <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>507</v>
       </c>
       <c r="G2" t="s">
-        <v>194</v>
+        <v>508</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -4201,27 +4166,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>509</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>510</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>511</v>
       </c>
       <c r="D3" t="s">
         <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>198</v>
+        <v>512</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>513</v>
       </c>
       <c r="G3" t="s">
-        <v>200</v>
+        <v>514</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -4245,159 +4210,159 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>515</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>517</v>
       </c>
       <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>518</v>
+      </c>
+      <c r="F4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G4" t="s">
+        <v>520</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>521</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" t="s">
+        <v>522</v>
+      </c>
+      <c r="F5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G5" t="s">
+        <v>523</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C6" t="s">
+        <v>526</v>
+      </c>
+      <c r="D6" t="s">
         <v>155</v>
       </c>
-      <c r="E4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G4" t="s">
-        <v>206</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F6" t="s">
+        <v>528</v>
+      </c>
+      <c r="G6" t="s">
+        <v>529</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>530</v>
+      </c>
+      <c r="B7" t="s">
+        <v>531</v>
+      </c>
+      <c r="C7" t="s">
+        <v>532</v>
+      </c>
+      <c r="D7" t="s">
         <v>155</v>
       </c>
-      <c r="E5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" t="s">
-        <v>212</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" t="s">
-        <v>214</v>
-      </c>
-      <c r="C6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F6" t="s">
-        <v>217</v>
-      </c>
-      <c r="G6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" t="s">
-        <v>168</v>
-      </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>533</v>
       </c>
       <c r="F7" t="s">
-        <v>223</v>
+        <v>534</v>
       </c>
       <c r="G7" t="s">
-        <v>224</v>
+        <v>535</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -4421,27 +4386,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>536</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>386</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>537</v>
       </c>
       <c r="D8" t="s">
         <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>228</v>
+        <v>512</v>
       </c>
       <c r="F8" t="s">
-        <v>229</v>
+        <v>538</v>
       </c>
       <c r="G8" t="s">
-        <v>230</v>
+        <v>539</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -4465,15 +4430,193 @@
         <v>145</v>
       </c>
     </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>540</v>
+      </c>
+      <c r="B9" t="s">
+        <v>541</v>
+      </c>
+      <c r="C9" t="s">
+        <v>542</v>
+      </c>
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
+        <v>543</v>
+      </c>
+      <c r="F9" t="s">
+        <v>544</v>
+      </c>
+      <c r="G9" t="s">
+        <v>545</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>546</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" t="s">
+        <v>548</v>
+      </c>
+      <c r="F10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G10" t="s">
+        <v>549</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>550</v>
+      </c>
+      <c r="B11" t="s">
+        <v>551</v>
+      </c>
+      <c r="C11" t="s">
+        <v>552</v>
+      </c>
+      <c r="D11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" t="s">
+        <v>553</v>
+      </c>
+      <c r="F11" t="s">
+        <v>554</v>
+      </c>
+      <c r="G11" t="s">
+        <v>555</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B12" t="s">
+        <v>557</v>
+      </c>
+      <c r="C12" t="s">
+        <v>558</v>
+      </c>
+      <c r="D12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" t="s">
+        <v>518</v>
+      </c>
+      <c r="F12" t="s">
+        <v>559</v>
+      </c>
+      <c r="G12" t="s">
+        <v>560</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658632A5-EB87-48AA-B003-D1FCA09AC873}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -4517,15 +4660,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>561</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>562</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>563</v>
       </c>
       <c r="D2" t="s">
         <v>141</v>
@@ -4534,10 +4677,10 @@
         <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>234</v>
+        <v>564</v>
       </c>
       <c r="G2" t="s">
-        <v>235</v>
+        <v>565</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -4561,27 +4704,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>566</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>567</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>568</v>
       </c>
       <c r="D3" t="s">
         <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>239</v>
+        <v>569</v>
       </c>
       <c r="F3" t="s">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="G3" t="s">
-        <v>241</v>
+        <v>571</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -4605,27 +4748,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>572</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>573</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>574</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>245</v>
+        <v>569</v>
       </c>
       <c r="F4" t="s">
-        <v>246</v>
+        <v>575</v>
       </c>
       <c r="G4" t="s">
-        <v>247</v>
+        <v>576</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -4649,27 +4792,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>248</v>
+        <v>577</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>398</v>
       </c>
       <c r="C5" t="s">
-        <v>250</v>
+        <v>578</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>579</v>
       </c>
       <c r="F5" t="s">
-        <v>252</v>
+        <v>354</v>
       </c>
       <c r="G5" t="s">
-        <v>253</v>
+        <v>580</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -4693,27 +4836,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>581</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>582</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>583</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>569</v>
       </c>
       <c r="F6" t="s">
-        <v>257</v>
+        <v>584</v>
       </c>
       <c r="G6" t="s">
-        <v>258</v>
+        <v>585</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -4737,27 +4880,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>586</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>587</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>588</v>
       </c>
       <c r="D7" t="s">
         <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>262</v>
+        <v>589</v>
       </c>
       <c r="F7" t="s">
-        <v>263</v>
+        <v>590</v>
       </c>
       <c r="G7" t="s">
-        <v>264</v>
+        <v>591</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -4781,15 +4924,105 @@
         <v>145</v>
       </c>
     </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>592</v>
+      </c>
+      <c r="B8" t="s">
+        <v>593</v>
+      </c>
+      <c r="C8" t="s">
+        <v>594</v>
+      </c>
+      <c r="D8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" t="s">
+        <v>595</v>
+      </c>
+      <c r="F8" t="s">
+        <v>596</v>
+      </c>
+      <c r="G8" t="s">
+        <v>597</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>598</v>
+      </c>
+      <c r="B9" t="s">
+        <v>599</v>
+      </c>
+      <c r="C9" t="s">
+        <v>600</v>
+      </c>
+      <c r="D9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" t="s">
+        <v>569</v>
+      </c>
+      <c r="F9" t="s">
+        <v>601</v>
+      </c>
+      <c r="G9" t="s">
+        <v>602</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F437C0-5663-4D04-84A8-2C7EF4EAA719}">
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -4833,15 +5066,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>603</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>604</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>605</v>
       </c>
       <c r="D2" t="s">
         <v>141</v>
@@ -4850,10 +5083,10 @@
         <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>268</v>
+        <v>606</v>
       </c>
       <c r="G2" t="s">
-        <v>269</v>
+        <v>607</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -4877,27 +5110,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>608</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>609</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>610</v>
       </c>
       <c r="D3" t="s">
         <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>273</v>
+        <v>611</v>
       </c>
       <c r="F3" t="s">
-        <v>274</v>
+        <v>612</v>
       </c>
       <c r="G3" t="s">
-        <v>275</v>
+        <v>613</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -4921,27 +5154,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>614</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>615</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>616</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>279</v>
+        <v>617</v>
       </c>
       <c r="F4" t="s">
-        <v>280</v>
+        <v>618</v>
       </c>
       <c r="G4" t="s">
-        <v>281</v>
+        <v>619</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -4965,27 +5198,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>620</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>621</v>
       </c>
       <c r="C5" t="s">
-        <v>284</v>
+        <v>622</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>623</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>624</v>
       </c>
       <c r="G5" t="s">
-        <v>286</v>
+        <v>625</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -5009,27 +5242,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>626</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>627</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>628</v>
       </c>
       <c r="D6" t="s">
         <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>629</v>
       </c>
       <c r="F6" t="s">
-        <v>290</v>
+        <v>630</v>
       </c>
       <c r="G6" t="s">
-        <v>291</v>
+        <v>631</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -5053,27 +5286,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>292</v>
+        <v>632</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>633</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>634</v>
       </c>
       <c r="D7" t="s">
         <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>635</v>
       </c>
       <c r="F7" t="s">
-        <v>295</v>
+        <v>636</v>
       </c>
       <c r="G7" t="s">
-        <v>296</v>
+        <v>637</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -5097,387 +5330,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>638</v>
       </c>
       <c r="B8" t="s">
-        <v>298</v>
+        <v>639</v>
       </c>
       <c r="C8" t="s">
-        <v>299</v>
-      </c>
-      <c r="D8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" t="s">
-        <v>300</v>
-      </c>
-      <c r="F8" t="s">
-        <v>301</v>
-      </c>
-      <c r="G8" t="s">
-        <v>302</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B4" t="s">
-        <v>315</v>
-      </c>
-      <c r="C4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s">
-        <v>317</v>
-      </c>
-      <c r="F4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G4" t="s">
-        <v>319</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C5" t="s">
-        <v>322</v>
-      </c>
-      <c r="D5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" t="s">
-        <v>323</v>
-      </c>
-      <c r="F5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G5" t="s">
-        <v>325</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" t="s">
-        <v>329</v>
-      </c>
-      <c r="F6" t="s">
-        <v>330</v>
-      </c>
-      <c r="G6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>332</v>
-      </c>
-      <c r="B7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C7" t="s">
-        <v>334</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>335</v>
-      </c>
-      <c r="F7" t="s">
-        <v>336</v>
-      </c>
-      <c r="G7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>338</v>
-      </c>
-      <c r="B8" t="s">
-        <v>339</v>
-      </c>
-      <c r="C8" t="s">
-        <v>340</v>
+        <v>574</v>
       </c>
       <c r="D8" t="s">
         <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>635</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>640</v>
       </c>
       <c r="G8" t="s">
-        <v>343</v>
+        <v>641</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -5501,475 +5374,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>344</v>
-      </c>
-      <c r="B9" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" t="s">
-        <v>346</v>
-      </c>
-      <c r="D9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" t="s">
-        <v>347</v>
-      </c>
-      <c r="F9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G9" t="s">
-        <v>349</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>350</v>
-      </c>
-      <c r="B10" t="s">
-        <v>351</v>
-      </c>
-      <c r="C10" t="s">
-        <v>352</v>
-      </c>
-      <c r="D10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" t="s">
-        <v>353</v>
-      </c>
-      <c r="F10" t="s">
-        <v>354</v>
-      </c>
-      <c r="G10" t="s">
-        <v>355</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G2" t="s">
-        <v>360</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>364</v>
-      </c>
-      <c r="F3" t="s">
-        <v>365</v>
-      </c>
-      <c r="G3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F4" t="s">
-        <v>371</v>
-      </c>
-      <c r="G4" t="s">
-        <v>372</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>373</v>
-      </c>
-      <c r="B5" t="s">
-        <v>374</v>
-      </c>
-      <c r="C5" t="s">
-        <v>375</v>
-      </c>
-      <c r="D5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" t="s">
-        <v>376</v>
-      </c>
-      <c r="F5" t="s">
-        <v>377</v>
-      </c>
-      <c r="G5" t="s">
-        <v>378</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>379</v>
-      </c>
-      <c r="B6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" t="s">
-        <v>382</v>
-      </c>
-      <c r="F6" t="s">
-        <v>383</v>
-      </c>
-      <c r="G6" t="s">
-        <v>384</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>385</v>
-      </c>
-      <c r="B7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G7" t="s">
-        <v>390</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>391</v>
-      </c>
-      <c r="B8" t="s">
-        <v>392</v>
-      </c>
-      <c r="C8" t="s">
-        <v>393</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" t="s">
-        <v>394</v>
-      </c>
-      <c r="F8" t="s">
-        <v>395</v>
-      </c>
-      <c r="G8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>397</v>
+        <v>642</v>
       </c>
       <c r="B9" t="s">
         <v>398</v>
       </c>
       <c r="C9" t="s">
-        <v>399</v>
+        <v>643</v>
       </c>
       <c r="D9" t="s">
         <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>400</v>
+        <v>644</v>
       </c>
       <c r="F9" t="s">
         <v>354</v>
       </c>
       <c r="G9" t="s">
-        <v>401</v>
+        <v>645</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -5993,27 +5418,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>402</v>
+        <v>646</v>
       </c>
       <c r="B10" t="s">
-        <v>403</v>
+        <v>647</v>
       </c>
       <c r="C10" t="s">
-        <v>404</v>
+        <v>648</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>364</v>
+        <v>649</v>
       </c>
       <c r="F10" t="s">
-        <v>405</v>
+        <v>650</v>
       </c>
       <c r="G10" t="s">
-        <v>406</v>
+        <v>651</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -6037,1371 +5462,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>652</v>
       </c>
       <c r="B11" t="s">
-        <v>408</v>
+        <v>653</v>
       </c>
       <c r="C11" t="s">
-        <v>409</v>
-      </c>
-      <c r="D11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" t="s">
-        <v>410</v>
-      </c>
-      <c r="F11" t="s">
-        <v>411</v>
-      </c>
-      <c r="G11" t="s">
-        <v>412</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>413</v>
-      </c>
-      <c r="B12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C12" t="s">
-        <v>415</v>
-      </c>
-      <c r="D12" t="s">
-        <v>155</v>
-      </c>
-      <c r="E12" t="s">
-        <v>416</v>
-      </c>
-      <c r="F12" t="s">
-        <v>417</v>
-      </c>
-      <c r="G12" t="s">
-        <v>418</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G2" t="s">
-        <v>423</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>424</v>
-      </c>
-      <c r="B3" t="s">
-        <v>425</v>
-      </c>
-      <c r="C3" t="s">
-        <v>426</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F3" t="s">
-        <v>428</v>
-      </c>
-      <c r="G3" t="s">
-        <v>429</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F4" t="s">
-        <v>432</v>
-      </c>
-      <c r="G4" t="s">
-        <v>433</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>434</v>
-      </c>
-      <c r="B5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C5" t="s">
-        <v>435</v>
-      </c>
-      <c r="D5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" t="s">
-        <v>436</v>
-      </c>
-      <c r="F5" t="s">
-        <v>437</v>
-      </c>
-      <c r="G5" t="s">
-        <v>438</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>439</v>
-      </c>
-      <c r="B6" t="s">
-        <v>440</v>
-      </c>
-      <c r="C6" t="s">
-        <v>441</v>
-      </c>
-      <c r="D6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" t="s">
-        <v>410</v>
-      </c>
-      <c r="F6" t="s">
-        <v>442</v>
-      </c>
-      <c r="G6" t="s">
-        <v>443</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>444</v>
-      </c>
-      <c r="B7" t="s">
-        <v>445</v>
-      </c>
-      <c r="C7" t="s">
-        <v>446</v>
-      </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" t="s">
-        <v>447</v>
-      </c>
-      <c r="F7" t="s">
-        <v>448</v>
-      </c>
-      <c r="G7" t="s">
-        <v>449</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>450</v>
-      </c>
-      <c r="B8" t="s">
-        <v>398</v>
-      </c>
-      <c r="C8" t="s">
-        <v>451</v>
-      </c>
-      <c r="D8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" t="s">
-        <v>452</v>
-      </c>
-      <c r="F8" t="s">
-        <v>354</v>
-      </c>
-      <c r="G8" t="s">
-        <v>453</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>454</v>
-      </c>
-      <c r="B9" t="s">
-        <v>455</v>
-      </c>
-      <c r="C9" t="s">
-        <v>456</v>
-      </c>
-      <c r="D9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" t="s">
-        <v>410</v>
-      </c>
-      <c r="F9" t="s">
-        <v>457</v>
-      </c>
-      <c r="G9" t="s">
-        <v>458</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>459</v>
-      </c>
-      <c r="B10" t="s">
-        <v>460</v>
-      </c>
-      <c r="C10" t="s">
-        <v>461</v>
-      </c>
-      <c r="D10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" t="s">
-        <v>462</v>
-      </c>
-      <c r="F10" t="s">
-        <v>463</v>
-      </c>
-      <c r="G10" t="s">
-        <v>464</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N8"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>465</v>
-      </c>
-      <c r="B2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G2" t="s">
-        <v>469</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C3" t="s">
-        <v>472</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>473</v>
-      </c>
-      <c r="F3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G3" t="s">
-        <v>475</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>476</v>
-      </c>
-      <c r="B4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" t="s">
-        <v>477</v>
-      </c>
-      <c r="D4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" t="s">
-        <v>478</v>
-      </c>
-      <c r="F4" t="s">
-        <v>479</v>
-      </c>
-      <c r="G4" t="s">
-        <v>480</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>481</v>
-      </c>
-      <c r="B5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C5" t="s">
-        <v>483</v>
-      </c>
-      <c r="D5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" t="s">
-        <v>484</v>
-      </c>
-      <c r="F5" t="s">
-        <v>485</v>
-      </c>
-      <c r="G5" t="s">
-        <v>486</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>487</v>
-      </c>
-      <c r="B6" t="s">
-        <v>488</v>
-      </c>
-      <c r="C6" t="s">
-        <v>489</v>
-      </c>
-      <c r="D6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" t="s">
-        <v>490</v>
-      </c>
-      <c r="F6" t="s">
-        <v>491</v>
-      </c>
-      <c r="G6" t="s">
-        <v>492</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>493</v>
-      </c>
-      <c r="B7" t="s">
-        <v>494</v>
-      </c>
-      <c r="C7" t="s">
-        <v>495</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G7" t="s">
-        <v>498</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>499</v>
-      </c>
-      <c r="B8" t="s">
-        <v>500</v>
-      </c>
-      <c r="C8" t="s">
-        <v>501</v>
-      </c>
-      <c r="D8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" t="s">
-        <v>410</v>
-      </c>
-      <c r="F8" t="s">
-        <v>502</v>
-      </c>
-      <c r="G8" t="s">
-        <v>503</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>507</v>
-      </c>
-      <c r="G2" t="s">
-        <v>508</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C3" t="s">
-        <v>511</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>512</v>
-      </c>
-      <c r="F3" t="s">
-        <v>513</v>
-      </c>
-      <c r="G3" t="s">
-        <v>514</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>515</v>
-      </c>
-      <c r="B4" t="s">
-        <v>516</v>
-      </c>
-      <c r="C4" t="s">
-        <v>517</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s">
-        <v>518</v>
-      </c>
-      <c r="F4" t="s">
-        <v>519</v>
-      </c>
-      <c r="G4" t="s">
-        <v>520</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>521</v>
-      </c>
-      <c r="B5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C5" t="s">
-        <v>369</v>
-      </c>
-      <c r="D5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5" t="s">
-        <v>522</v>
-      </c>
-      <c r="F5" t="s">
-        <v>432</v>
-      </c>
-      <c r="G5" t="s">
-        <v>523</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>524</v>
-      </c>
-      <c r="B6" t="s">
-        <v>525</v>
-      </c>
-      <c r="C6" t="s">
-        <v>526</v>
-      </c>
-      <c r="D6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E6" t="s">
-        <v>527</v>
-      </c>
-      <c r="F6" t="s">
-        <v>528</v>
-      </c>
-      <c r="G6" t="s">
-        <v>529</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>530</v>
-      </c>
-      <c r="B7" t="s">
-        <v>531</v>
-      </c>
-      <c r="C7" t="s">
-        <v>532</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>533</v>
-      </c>
-      <c r="F7" t="s">
-        <v>534</v>
-      </c>
-      <c r="G7" t="s">
-        <v>535</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>536</v>
-      </c>
-      <c r="B8" t="s">
-        <v>386</v>
-      </c>
-      <c r="C8" t="s">
-        <v>537</v>
-      </c>
-      <c r="D8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" t="s">
-        <v>512</v>
-      </c>
-      <c r="F8" t="s">
-        <v>538</v>
-      </c>
-      <c r="G8" t="s">
-        <v>539</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>540</v>
-      </c>
-      <c r="B9" t="s">
-        <v>541</v>
-      </c>
-      <c r="C9" t="s">
-        <v>542</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>543</v>
-      </c>
-      <c r="F9" t="s">
-        <v>544</v>
-      </c>
-      <c r="G9" t="s">
-        <v>545</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>546</v>
-      </c>
-      <c r="B10" t="s">
-        <v>398</v>
-      </c>
-      <c r="C10" t="s">
-        <v>547</v>
-      </c>
-      <c r="D10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" t="s">
-        <v>548</v>
-      </c>
-      <c r="F10" t="s">
-        <v>354</v>
-      </c>
-      <c r="G10" t="s">
-        <v>549</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>550</v>
-      </c>
-      <c r="B11" t="s">
-        <v>551</v>
-      </c>
-      <c r="C11" t="s">
-        <v>552</v>
+        <v>654</v>
       </c>
       <c r="D11" t="s">
         <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>553</v>
+        <v>655</v>
       </c>
       <c r="F11" t="s">
-        <v>554</v>
+        <v>656</v>
       </c>
       <c r="G11" t="s">
-        <v>555</v>
+        <v>657</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -7425,27 +5506,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>556</v>
+        <v>658</v>
       </c>
       <c r="B12" t="s">
-        <v>557</v>
+        <v>659</v>
       </c>
       <c r="C12" t="s">
-        <v>558</v>
+        <v>594</v>
       </c>
       <c r="D12" t="s">
         <v>168</v>
       </c>
       <c r="E12" t="s">
-        <v>518</v>
+        <v>595</v>
       </c>
       <c r="F12" t="s">
-        <v>559</v>
+        <v>660</v>
       </c>
       <c r="G12" t="s">
-        <v>560</v>
+        <v>661</v>
       </c>
       <c r="H12" t="s">
         <v>1</v>
@@ -7470,415 +5551,12 @@
       </c>
     </row>
   </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N9"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>561</v>
-      </c>
-      <c r="B2" t="s">
-        <v>562</v>
-      </c>
-      <c r="C2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>564</v>
-      </c>
-      <c r="G2" t="s">
-        <v>565</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C3" t="s">
-        <v>568</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F3" t="s">
-        <v>570</v>
-      </c>
-      <c r="G3" t="s">
-        <v>571</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>572</v>
-      </c>
-      <c r="B4" t="s">
-        <v>573</v>
-      </c>
-      <c r="C4" t="s">
-        <v>574</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" t="s">
-        <v>569</v>
-      </c>
-      <c r="F4" t="s">
-        <v>575</v>
-      </c>
-      <c r="G4" t="s">
-        <v>576</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>577</v>
-      </c>
-      <c r="B5" t="s">
-        <v>398</v>
-      </c>
-      <c r="C5" t="s">
-        <v>578</v>
-      </c>
-      <c r="D5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" t="s">
-        <v>579</v>
-      </c>
-      <c r="F5" t="s">
-        <v>354</v>
-      </c>
-      <c r="G5" t="s">
-        <v>580</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>581</v>
-      </c>
-      <c r="B6" t="s">
-        <v>582</v>
-      </c>
-      <c r="C6" t="s">
-        <v>583</v>
-      </c>
-      <c r="D6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" t="s">
-        <v>569</v>
-      </c>
-      <c r="F6" t="s">
-        <v>584</v>
-      </c>
-      <c r="G6" t="s">
-        <v>585</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>586</v>
-      </c>
-      <c r="B7" t="s">
-        <v>587</v>
-      </c>
-      <c r="C7" t="s">
-        <v>588</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>589</v>
-      </c>
-      <c r="F7" t="s">
-        <v>590</v>
-      </c>
-      <c r="G7" t="s">
-        <v>591</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>592</v>
-      </c>
-      <c r="B8" t="s">
-        <v>593</v>
-      </c>
-      <c r="C8" t="s">
-        <v>594</v>
-      </c>
-      <c r="D8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" t="s">
-        <v>595</v>
-      </c>
-      <c r="F8" t="s">
-        <v>596</v>
-      </c>
-      <c r="G8" t="s">
-        <v>597</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>598</v>
-      </c>
-      <c r="B9" t="s">
-        <v>599</v>
-      </c>
-      <c r="C9" t="s">
-        <v>600</v>
-      </c>
-      <c r="D9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" t="s">
-        <v>569</v>
-      </c>
-      <c r="F9" t="s">
-        <v>601</v>
-      </c>
-      <c r="G9" t="s">
-        <v>602</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF23AB6-6DE5-43C7-BF70-2B9BADB63F04}">
   <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -8327,11 +6005,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N12"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908B8797-355C-4B71-848F-6D9C980007D6}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -8375,15 +6054,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>603</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>604</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>605</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
         <v>141</v>
@@ -8392,10 +6071,10 @@
         <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>606</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>607</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -8419,27 +6098,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>608</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>609</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>610</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
         <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>611</v>
+        <v>149</v>
       </c>
       <c r="F3" t="s">
-        <v>612</v>
+        <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>613</v>
+        <v>151</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -8463,27 +6142,799 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>614</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>615</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>616</v>
+        <v>154</v>
+      </c>
+      <c r="D4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DBFD15-2CEB-4627-A876-8778177346FC}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="48.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="30.77734375" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="144" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B00EE4-657F-4C77-979E-871B50CE11EA}">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" t="s">
+        <v>244</v>
       </c>
       <c r="D4" t="s">
         <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>617</v>
+        <v>245</v>
       </c>
       <c r="F4" t="s">
-        <v>618</v>
+        <v>246</v>
       </c>
       <c r="G4" t="s">
-        <v>619</v>
+        <v>247</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
@@ -8507,27 +6958,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>620</v>
+        <v>248</v>
       </c>
       <c r="B5" t="s">
-        <v>621</v>
+        <v>249</v>
       </c>
       <c r="C5" t="s">
-        <v>622</v>
+        <v>250</v>
       </c>
       <c r="D5" t="s">
         <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>623</v>
+        <v>251</v>
       </c>
       <c r="F5" t="s">
-        <v>624</v>
+        <v>252</v>
       </c>
       <c r="G5" t="s">
-        <v>625</v>
+        <v>253</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -8551,27 +7002,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>626</v>
+        <v>254</v>
       </c>
       <c r="B6" t="s">
-        <v>627</v>
+        <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>628</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
         <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>629</v>
+        <v>256</v>
       </c>
       <c r="F6" t="s">
-        <v>630</v>
+        <v>257</v>
       </c>
       <c r="G6" t="s">
-        <v>631</v>
+        <v>258</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -8595,27 +7046,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>632</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s">
-        <v>633</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>634</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
         <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>635</v>
+        <v>262</v>
       </c>
       <c r="F7" t="s">
-        <v>636</v>
+        <v>263</v>
       </c>
       <c r="G7" t="s">
-        <v>637</v>
+        <v>264</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
@@ -8639,27 +7090,707 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8907D456-B997-458B-8955-1847D2DA6719}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" t="s">
+        <v>285</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>638</v>
+        <v>297</v>
       </c>
       <c r="B8" t="s">
-        <v>639</v>
+        <v>298</v>
       </c>
       <c r="C8" t="s">
-        <v>574</v>
+        <v>299</v>
+      </c>
+      <c r="D8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F566A42-FF84-4BE8-837C-4E9F24929697}">
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" t="s">
+        <v>319</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G6" t="s">
+        <v>331</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F7" t="s">
+        <v>336</v>
+      </c>
+      <c r="G7" t="s">
+        <v>337</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" t="s">
+        <v>340</v>
       </c>
       <c r="D8" t="s">
         <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>635</v>
+        <v>341</v>
       </c>
       <c r="F8" t="s">
-        <v>640</v>
+        <v>342</v>
       </c>
       <c r="G8" t="s">
-        <v>641</v>
+        <v>343</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
@@ -8683,27 +7814,477 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>642</v>
+        <v>344</v>
+      </c>
+      <c r="B9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F9" t="s">
+        <v>348</v>
+      </c>
+      <c r="G9" t="s">
+        <v>349</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>350</v>
+      </c>
+      <c r="B10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F10" t="s">
+        <v>354</v>
+      </c>
+      <c r="G10" t="s">
+        <v>355</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FE3881-CFD1-4827-BEC6-2956805AAA01}">
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G3" t="s">
+        <v>366</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>370</v>
+      </c>
+      <c r="F4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" t="s">
+        <v>382</v>
+      </c>
+      <c r="F6" t="s">
+        <v>383</v>
+      </c>
+      <c r="G6" t="s">
+        <v>384</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F7" t="s">
+        <v>389</v>
+      </c>
+      <c r="G7" t="s">
+        <v>390</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" t="s">
+        <v>395</v>
+      </c>
+      <c r="G8" t="s">
+        <v>396</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>397</v>
       </c>
       <c r="B9" t="s">
         <v>398</v>
       </c>
       <c r="C9" t="s">
-        <v>643</v>
+        <v>399</v>
       </c>
       <c r="D9" t="s">
         <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>644</v>
+        <v>400</v>
       </c>
       <c r="F9" t="s">
         <v>354</v>
       </c>
       <c r="G9" t="s">
-        <v>645</v>
+        <v>401</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -8727,27 +8308,565 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>646</v>
+        <v>402</v>
       </c>
       <c r="B10" t="s">
-        <v>647</v>
+        <v>403</v>
       </c>
       <c r="C10" t="s">
-        <v>648</v>
+        <v>404</v>
       </c>
       <c r="D10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" t="s">
+        <v>364</v>
+      </c>
+      <c r="F10" t="s">
+        <v>405</v>
+      </c>
+      <c r="G10" t="s">
+        <v>406</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>407</v>
+      </c>
+      <c r="B11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F11" t="s">
+        <v>411</v>
+      </c>
+      <c r="G11" t="s">
+        <v>412</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C12" t="s">
+        <v>415</v>
+      </c>
+      <c r="D12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" t="s">
+        <v>416</v>
+      </c>
+      <c r="F12" t="s">
+        <v>417</v>
+      </c>
+      <c r="G12" t="s">
+        <v>418</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECC9F61-17AB-46AD-BA87-F58B90DEAF47}">
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2" t="s">
         <v>141</v>
       </c>
+      <c r="E2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G2" t="s">
+        <v>423</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>434</v>
+      </c>
+      <c r="B5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F5" t="s">
+        <v>437</v>
+      </c>
+      <c r="G5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" t="s">
+        <v>440</v>
+      </c>
+      <c r="C6" t="s">
+        <v>441</v>
+      </c>
+      <c r="D6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" t="s">
+        <v>410</v>
+      </c>
+      <c r="F6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G6" t="s">
+        <v>443</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" t="s">
+        <v>447</v>
+      </c>
+      <c r="F7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G7" t="s">
+        <v>449</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>450</v>
+      </c>
+      <c r="B8" t="s">
+        <v>398</v>
+      </c>
+      <c r="C8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F8" t="s">
+        <v>354</v>
+      </c>
+      <c r="G8" t="s">
+        <v>453</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>454</v>
+      </c>
+      <c r="B9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9" t="s">
+        <v>456</v>
+      </c>
+      <c r="D9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" t="s">
+        <v>410</v>
+      </c>
+      <c r="F9" t="s">
+        <v>457</v>
+      </c>
+      <c r="G9" t="s">
+        <v>458</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B10" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" t="s">
+        <v>168</v>
+      </c>
       <c r="E10" t="s">
-        <v>649</v>
+        <v>462</v>
       </c>
       <c r="F10" t="s">
-        <v>650</v>
+        <v>463</v>
       </c>
       <c r="G10" t="s">
-        <v>651</v>
+        <v>464</v>
       </c>
       <c r="H10" t="s">
         <v>1</v>
@@ -8771,94 +8890,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>652</v>
-      </c>
-      <c r="B11" t="s">
-        <v>653</v>
-      </c>
-      <c r="C11" t="s">
-        <v>654</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>655</v>
-      </c>
-      <c r="F11" t="s">
-        <v>656</v>
-      </c>
-      <c r="G11" t="s">
-        <v>657</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>658</v>
-      </c>
-      <c r="B12" t="s">
-        <v>659</v>
-      </c>
-      <c r="C12" t="s">
-        <v>594</v>
-      </c>
-      <c r="D12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" t="s">
-        <v>595</v>
-      </c>
-      <c r="F12" t="s">
-        <v>660</v>
-      </c>
-      <c r="G12" t="s">
-        <v>661</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>